--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\MMM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{488E3218-9FDE-4F87-AD51-3FC0B8BFCC96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC88477E-A8A8-4D22-A03E-2CE00F79E8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D900B509-3F45-437C-AF73-4D1CCE0A3090}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Date</t>
   </si>
@@ -37,6 +37,9 @@
   </si>
   <si>
     <t>Adstock &amp; Hill Transformation</t>
+  </si>
+  <si>
+    <t>Code Review (Priors Creation)</t>
   </si>
 </sst>
 </file>
@@ -404,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FECB7FC1-E18C-4501-9E6F-87E3EA02DF2B}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25.77734375" bestFit="1" customWidth="1"/>
@@ -434,6 +437,14 @@
         <v>3</v>
       </c>
     </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>46159</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\MMM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC88477E-A8A8-4D22-A03E-2CE00F79E8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C17BE0B7-E030-47E6-952F-0BF961F6D75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D900B509-3F45-437C-AF73-4D1CCE0A3090}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Date</t>
   </si>
@@ -39,7 +39,10 @@
     <t>Adstock &amp; Hill Transformation</t>
   </si>
   <si>
-    <t>Code Review (Priors Creation)</t>
+    <t>Code Review 1 (Priors Creation)</t>
+  </si>
+  <si>
+    <t>Code Review 2 (Priors Creation)</t>
   </si>
 </sst>
 </file>
@@ -100,8 +103,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4464659A-4291-483E-B19E-CF2C15A688A6}" name="Table1" displayName="Table1" ref="A1:B3" totalsRowShown="0">
-  <autoFilter ref="A1:B3" xr:uid="{4464659A-4291-483E-B19E-CF2C15A688A6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4464659A-4291-483E-B19E-CF2C15A688A6}" name="Table1" displayName="Table1" ref="A1:B4" totalsRowShown="0">
+  <autoFilter ref="A1:B4" xr:uid="{4464659A-4291-483E-B19E-CF2C15A688A6}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{38B7A78C-A21B-4C76-BF97-64D116023267}" name="Date" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{23517125-3416-4F31-B68F-BAA58FF83E8C}" name="Topic"/>
@@ -410,7 +413,7 @@
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -437,12 +440,20 @@
         <v>3</v>
       </c>
     </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+    </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46159</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\MMM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C17BE0B7-E030-47E6-952F-0BF961F6D75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199822B1-BB9E-46BC-AD40-FAFF48FC6407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D900B509-3F45-437C-AF73-4D1CCE0A3090}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Date</t>
   </si>
@@ -43,6 +43,9 @@
   </si>
   <si>
     <t>Code Review 2 (Priors Creation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L1 &amp; L2 </t>
   </si>
 </sst>
 </file>
@@ -410,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FECB7FC1-E18C-4501-9E6F-87E3EA02DF2B}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27.109375" bestFit="1" customWidth="1"/>
@@ -456,6 +459,14 @@
         <v>5</v>
       </c>
     </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>46172</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
